--- a/data/trans_bre/P1403-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1403-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>-13,21%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,81</t>
+          <t>-4,86; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 9,38</t>
+          <t>-2,25; 9,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 5,85</t>
+          <t>-6,17; 5,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,32</t>
+          <t>-7,96; 3,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 61,67</t>
+          <t>-30,62; 64,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 105,08</t>
+          <t>-15,82; 112,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 66,29</t>
+          <t>-41,95; 65,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 32,29</t>
+          <t>-32,04; 17,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-3,52%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,7</t>
+          <t>3,86; 11,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,09</t>
+          <t>-0,84; 8,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,73</t>
+          <t>1,06; 10,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,89</t>
+          <t>-5,33; 3,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 173,06</t>
+          <t>31,67; 160,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 64,73</t>
+          <t>-5,03; 67,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 76,25</t>
+          <t>5,81; 77,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 27,5</t>
+          <t>-26,98; 26,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,77</t>
+          <t>0,8; 12,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 10,66</t>
+          <t>-2,15; 10,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,73</t>
+          <t>-5,12; 5,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,35</t>
+          <t>-3,42; 6,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 109,57</t>
+          <t>4,74; 107,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 66,8</t>
+          <t>-10,2; 67,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 50,03</t>
+          <t>-29,1; 50,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 42,51</t>
+          <t>-14,86; 40,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,38%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 9,45</t>
+          <t>-1,71; 9,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 13,66</t>
+          <t>1,33; 13,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,15</t>
+          <t>-2,52; 9,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 4,3</t>
+          <t>-3,12; 8,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 78,96</t>
+          <t>-9,35; 76,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 88,34</t>
+          <t>6,01; 85,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 65,35</t>
+          <t>-12,51; 65,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 24,04</t>
+          <t>-14,04; 50,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 13,16</t>
+          <t>0,54; 13,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,95</t>
+          <t>3,52; 19,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 14,69</t>
+          <t>0,11; 14,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,49</t>
+          <t>-0,96; 10,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 247,68</t>
+          <t>2,15; 245,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 157,28</t>
+          <t>16,61; 171,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 163,99</t>
+          <t>-0,95; 163,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 55,79</t>
+          <t>-3,43; 55,46</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,96%</t>
+          <t>-10,77%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 10,3</t>
+          <t>-2,4; 10,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 6,69</t>
+          <t>-7,7; 6,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 9,52</t>
+          <t>-2,28; 9,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,89</t>
+          <t>-8,66; 2,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 91,15</t>
+          <t>-14,48; 84,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 35,45</t>
+          <t>-28,49; 36,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 89,77</t>
+          <t>-14,2; 87,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 8,44</t>
+          <t>-28,68; 11,85</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>125,79%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,12</t>
+          <t>-1,21; 7,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 8,53</t>
+          <t>-0,5; 8,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,12</t>
+          <t>-4,06; 4,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 51,59</t>
+          <t>-1,29; 7,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 57,61</t>
+          <t>-7,36; 59,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 52,38</t>
+          <t>-2,36; 51,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 33,81</t>
+          <t>-25,44; 36,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 340,57</t>
+          <t>-6,03; 43,87</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,99</t>
+          <t>-2,89; 4,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,33</t>
+          <t>-1,45; 5,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 6,91</t>
+          <t>-1,41; 6,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,31; 16,99</t>
+          <t>0,47; 7,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 33,6</t>
+          <t>-19,33; 36,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 52,29</t>
+          <t>-8,77; 47,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 46,97</t>
+          <t>-7,46; 44,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,26; 261,11</t>
+          <t>2,46; 49,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,75</t>
+          <t>2,31; 5,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,92</t>
+          <t>2,13; 5,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,33</t>
+          <t>0,75; 4,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 22,99</t>
+          <t>0,08; 3,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,76; 48,07</t>
+          <t>16,24; 47,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,86; 36,81</t>
+          <t>11,78; 37,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 30,04</t>
+          <t>4,7; 30,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,2; 139,52</t>
+          <t>0,36; 19,05</t>
         </is>
       </c>
     </row>
